--- a/fiches-techniques/DONNEES_PDC_Netair.xlsx
+++ b/fiches-techniques/DONNEES_PDC_Netair.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Données PDC R&amp;D" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Données PDC R&amp;D" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="E61" s="36" t="inlineStr">
         <is>
-          <t>Moléculaire (ISO 10121)</t>
+          <t>Moléculaire</t>
         </is>
       </c>
       <c r="F61" s="36" t="n">
@@ -5144,24 +5144,26 @@
         </is>
       </c>
       <c r="H61" s="37" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I61" s="37" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J61" s="37" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="L61" s="37" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="M61" s="37" t="n">
-        <v>103</v>
-      </c>
-      <c r="N61" s="37" t="n"/>
+        <v>128</v>
+      </c>
+      <c r="N61" s="37" t="n">
+        <v>155</v>
+      </c>
       <c r="O61" s="38">
         <f>IFERROR(IF(COUNT($H61:$N61)=7,INDEX(LINEST($H61:$N61,$H$6:$N$6^{1;2}),1,1),""),"")</f>
         <v/>
@@ -5192,7 +5194,7 @@
       </c>
       <c r="V61" s="36" t="inlineStr">
         <is>
-          <t>Dossier SV GD CARB : courbe 2020 'QL-CARB' (cohérente fiche 2018, axe Y 0-120). PIÈGE : fichiers F7/F8 2023 = copies du base 2023 [22..155] hors axe → écartés. Charbon → ΔP non colmatante.</t>
+          <t>Courbe 2023 retenue (décision PA 12/10/2026) : fiche SV-GD CARB 2023.pdf (créée 07/11/2024, classe ISO NA = charbon seul), 7 pts 0,79→3,17 m/s = 1 000→4 000 m³/h ; ΔP@3400 ≈ 121 Pa. Les fichiers F7/F8 2023 en sont des copies (version combinée non mesurée). Remplace la courbe 2020 [18,31,45,61,79,103 de 1 000 à 3 500] utilisée en v1.0. Charbon → ΔP non colmatante.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/DONNEES_PDC_Netair.xlsx
+++ b/fiches-techniques/DONNEES_PDC_Netair.xlsx
@@ -5221,7 +5221,7 @@
       </c>
       <c r="E62" s="36" t="inlineStr">
         <is>
-          <t>Moléculaire (ISO 10121)</t>
+          <t>Moléculaire</t>
         </is>
       </c>
       <c r="F62" s="36" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V62" s="36" t="inlineStr">
         <is>
-          <t>⚠ COURBE PARTAGÉE = pack charbon 292 mm de SV-GD/QL-CARB (l.61, AZUR). V-CARB n'a aucune courbe propre mesurée (doc = '85 Pa' plat). Courbe V-CARB À MESURER R&amp;D. Nominal V-CARB 3000.</t>
+          <t>⚠ AUCUNE COURBE AFFICHÉE depuis la v1.1 (décision PA 12/10/2026, clé sans_courbe) : pas de mesure du V-CARB charbon seul. Les valeurs de cette ligne = ancienne courbe empruntée QL-CARB 2013 (même que l'ancienne AZUR), conservées pour mémoire, NON UTILISÉES. Fiche V-CARB F7 2018 (combinée) = copie de QL-CARB F9 2013 → non fiable. Courbe V-CARB à obtenir du fournisseur.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/DONNEES_PDC_Netair.xlsx
+++ b/fiches-techniques/DONNEES_PDC_Netair.xlsx
@@ -5370,7 +5370,7 @@
       </c>
       <c r="V63" s="36" t="inlineStr">
         <is>
-          <t>TITABAG F9 CARB 2021 (cache Excel). COMBINÉ F9 ePM1 80% + charbon imprégné → COLMATANT, règle ePM +100 (PAS const). Capacité 15%. Cadre acier, 520mm.</t>
+          <t>⚠ NON UTILISÉE depuis la v1.1 (12/10/2026) : la fiche suit désormais la fiche fournisseur Deltricarb GCA (F7, ΔP 105/130/145 Pa par profondeur, pas de courbe). Ligne conservée pour mémoire = TITABAG F9 CA 2021 (F9, 520 mm, 47→284 Pa).</t>
         </is>
       </c>
     </row>
